--- a/HelperFiles/profiles/Example_Profile.xlsx
+++ b/HelperFiles/profiles/Example_Profile.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
